--- a/PC_2014/E__ScanF20_PC_027.xlsx
+++ b/PC_2014/E__ScanF20_PC_027.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,19 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +70,32 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +117,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +176,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,11 +560,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -522,117 +617,122 @@
           <t>PS_No</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>PS_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Chennamaneni Vidya Sagar Rao</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Ponnam Prabhakar</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Burla Ravi</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Byagari Laxman</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Vinod Kumar Boinapally</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Dr. Dharmaiah Vendavetla</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Lenkala Prabhakar Reddy</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Meesala Raji Reddy</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Ranaveni Lakshman</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Reddi Malla Srinivas</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Shaik Mohmood</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Uppuleti Laxman</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Kandem Prabhakar</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Pulikota Ramesh</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Mallesh Yadav Barla</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Mommed Amjad Mohiuddin</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Srinvas Reddy Lingampally</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Total_Valid_Votes</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Rejected_Votes</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>NOTA</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Checksum_Diff</t>
         </is>
@@ -642,8 +742,10 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Sarvareddipalli</t>
+        </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>0</v>
@@ -670,11 +772,11 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
@@ -694,11 +796,11 @@
         <v>0</v>
       </c>
       <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
@@ -709,15 +811,21 @@
         <v>0</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-478</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <f>SUM(C6:S6)-T6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Sarvareddipalli</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>0</v>
@@ -735,11 +843,11 @@
         <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
       </c>
@@ -783,15 +891,21 @@
         <v>0</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <f>SUM(C7:S7)-T7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Narsimulapalli</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>0</v>
@@ -848,24 +962,30 @@
         <v>0</v>
       </c>
       <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="X8" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <f>SUM(C8:S8)-T8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Burgupalli</t>
+        </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>0</v>
@@ -886,11 +1006,11 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
@@ -931,15 +1051,21 @@
         <v>0</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4">
+        <f>SUM(C9:S9)-T9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Kondaiahpalli</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>0</v>
@@ -975,11 +1101,11 @@
         <v>0</v>
       </c>
       <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
       </c>
@@ -993,11 +1119,11 @@
         <v>0</v>
       </c>
       <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V10" s="4" t="n">
         <v>0</v>
       </c>
@@ -1005,15 +1131,21 @@
         <v>0</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4">
+        <f>SUM(C10:S10)-T10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Velichala</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>0</v>
@@ -1080,53 +1212,59 @@
       </c>
       <c r="X11" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" s="4">
+        <f>SUM(C11:S11)-T11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Nomularajaiahpalli H/o Arnakonda</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>143</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="D12" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>13</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0</v>
@@ -1138,11 +1276,11 @@
         <v>0</v>
       </c>
       <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="n">
         <v>381</v>
       </c>
-      <c r="T12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
@@ -1153,101 +1291,284 @@
         <v>0</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4">
+        <f>SUM(C12:S12)-T12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="6">
-        <f>SUM(B6:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="6">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="C13" s="8">
         <f>SUM(C6:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="8">
         <f>SUM(D6:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="8">
         <f>SUM(E6:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="8">
         <f>SUM(F6:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="8">
         <f>SUM(G6:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="8">
         <f>SUM(H6:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="8">
         <f>SUM(I6:I12)</f>
         <v/>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="8">
         <f>SUM(J6:J12)</f>
         <v/>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="8">
         <f>SUM(K6:K12)</f>
         <v/>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="8">
         <f>SUM(L6:L12)</f>
         <v/>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="8">
         <f>SUM(M6:M12)</f>
         <v/>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="8">
         <f>SUM(N6:N12)</f>
         <v/>
       </c>
-      <c r="O13" s="6">
+      <c r="O13" s="8">
         <f>SUM(O6:O12)</f>
         <v/>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="8">
         <f>SUM(P6:P12)</f>
         <v/>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q13" s="8">
         <f>SUM(Q6:Q12)</f>
         <v/>
       </c>
-      <c r="R13" s="6">
+      <c r="R13" s="8">
         <f>SUM(R6:R12)</f>
         <v/>
       </c>
-      <c r="S13" s="6">
+      <c r="S13" s="8">
         <f>SUM(S6:S12)</f>
         <v/>
       </c>
-      <c r="T13" s="6">
+      <c r="T13" s="8">
         <f>SUM(T6:T12)</f>
         <v/>
       </c>
-      <c r="U13" s="6">
+      <c r="U13" s="8">
         <f>SUM(U6:U12)</f>
         <v/>
       </c>
-      <c r="V13" s="6">
+      <c r="V13" s="8">
         <f>SUM(V6:V12)</f>
         <v/>
       </c>
-      <c r="W13" s="6">
-        <f>SUM(W6:W12)</f>
+      <c r="W13" s="8">
+        <f>T13+U13</f>
+        <v/>
+      </c>
+      <c r="X13" s="8">
+        <f>SUM(X6:X12)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="8">
+        <f>SUM(C13:S13)-T13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="C15" s="12">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="12">
+        <f>D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>F13+F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="12">
+        <f>G13+G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="12">
+        <f>H13+H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="12">
+        <f>I13+I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="12">
+        <f>J13+J14</f>
+        <v/>
+      </c>
+      <c r="K15" s="12">
+        <f>K13+K14</f>
+        <v/>
+      </c>
+      <c r="L15" s="12">
+        <f>L13+L14</f>
+        <v/>
+      </c>
+      <c r="M15" s="12">
+        <f>M13+M14</f>
+        <v/>
+      </c>
+      <c r="N15" s="12">
+        <f>N13+N14</f>
+        <v/>
+      </c>
+      <c r="O15" s="12">
+        <f>O13+O14</f>
+        <v/>
+      </c>
+      <c r="P15" s="12">
+        <f>P13+P14</f>
+        <v/>
+      </c>
+      <c r="Q15" s="12">
+        <f>Q13+Q14</f>
+        <v/>
+      </c>
+      <c r="R15" s="12">
+        <f>R13+R14</f>
+        <v/>
+      </c>
+      <c r="S15" s="12">
+        <f>S13+S14</f>
+        <v/>
+      </c>
+      <c r="T15" s="12">
+        <f>T13+T14</f>
+        <v/>
+      </c>
+      <c r="U15" s="12">
+        <f>U13+U14</f>
+        <v/>
+      </c>
+      <c r="V15" s="12">
+        <f>V13+V14</f>
+        <v/>
+      </c>
+      <c r="W15" s="12">
+        <f>W13+W14</f>
+        <v/>
+      </c>
+      <c r="X15" s="12">
+        <f>X13+X14</f>
+        <v/>
+      </c>
+      <c r="Y15" s="12">
+        <f>SUM(C15:S15)-T15</f>
         <v/>
       </c>
     </row>
